--- a/ci-cd-merge-resolver/repoCollector/datasets/bucket4j.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/bucket4j.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,28 +44,22 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>8bd7c94ecc2cfd05c2c2250e0e53e117210a1cc2</t>
-  </si>
-  <si>
-    <t>d048bca44b4be04f62f51dced99e15b9d4250745</t>
-  </si>
-  <si>
-    <t>d0afc8880f74736ac85c4c17f589eb8e05fc50b4</t>
-  </si>
-  <si>
-    <t>ac108f103f231d3b320bb1465215e0398cebf0a8</t>
-  </si>
-  <si>
-    <t>d8d6e2fbf9e97ab05e3f49226c8a3450e26646f9</t>
-  </si>
-  <si>
-    <t>8a6333b2653ae17da6d32211260d4968a03cea78</t>
-  </si>
-  <si>
-    <t>5528087e14a2c350ef4b08e7cdfc9196103dee19</t>
-  </si>
-  <si>
-    <t>567171944a09ff9b8d55e7ed4bdfb5648d1d5ecb</t>
+    <t>e96b5607101631cdebad619ca9b2a28d9d3d6627</t>
+  </si>
+  <si>
+    <t>4e3a39f35e105b8f52a54ae6a2032c31f9a148a7</t>
+  </si>
+  <si>
+    <t>a29e71d208589904611df56473fd08f8e8f20ab5</t>
+  </si>
+  <si>
+    <t>4572582d50ac9a035c5a3c85cd7752d1f9a92afc</t>
+  </si>
+  <si>
+    <t>a7f9135ca5e13b4f5644f55209bcdb2e089853f3</t>
+  </si>
+  <si>
+    <t>490a92b5656ef9953327cdfab3dbfaf56ec6ed13</t>
   </si>
   <si>
     <t>70d28dd27ad6a77ce87962ecf299ddcc6d4a878e</t>
@@ -77,6 +71,15 @@
     <t>849f2555955234ed602c017794681a28d46a2cc6</t>
   </si>
   <si>
+    <t>4c45116ce89f8d5f3ce90c966bffed34904f1424</t>
+  </si>
+  <si>
+    <t>15f2b26355a528b7bcd0f8bfa3c7145e03dcdbac</t>
+  </si>
+  <si>
+    <t>09dcfa13fa9ae8982f7b803265b584d27a3fcf6b</t>
+  </si>
+  <si>
     <t>51e9501483e68e78ec6f908843d20ff4b01f0002</t>
   </si>
   <si>
@@ -92,6 +95,15 @@
     <t>cb99eadd5ec21f4f099f7e7c098e2457ef3dc64e</t>
   </si>
   <si>
+    <t>387eaabe096806d63b81c417cf910d5eab8b40cc</t>
+  </si>
+  <si>
+    <t>e4631cf1e2c4e113d379d648e1d89ccba4ff2681</t>
+  </si>
+  <si>
+    <t>5d470fbf21017b88af701c893aadc695fce31a10</t>
+  </si>
+  <si>
     <t>9150817f0a0899a67b5dee2e1469dc3b3a1727f6</t>
   </si>
   <si>
@@ -101,13 +113,13 @@
     <t>4cbc154c16dd5e5a94d7448fe8c0415e1d5a81da</t>
   </si>
   <si>
-    <t>387eaabe096806d63b81c417cf910d5eab8b40cc</t>
-  </si>
-  <si>
-    <t>e4631cf1e2c4e113d379d648e1d89ccba4ff2681</t>
-  </si>
-  <si>
-    <t>5d470fbf21017b88af701c893aadc695fce31a10</t>
+    <t>438736d1705156655ab601e4a6307c9f10191ecc</t>
+  </si>
+  <si>
+    <t>83392f07e4a523055f49d0ff216e191be64ef745</t>
+  </si>
+  <si>
+    <t>e937936232e3c4c7842dff75bc4c1bf9b7d7a2d8</t>
   </si>
   <si>
     <t>dff58ac23a478a503311aca7507fd7276a3f2948</t>
@@ -161,7 +173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -207,10 +219,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>45.0</v>
+        <v>35.0</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>22.0</v>
@@ -222,10 +234,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>31.933998107910156</v>
+        <v>20.599000930786133</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -239,13 +251,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -254,10 +266,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>32.26100158691406</v>
+        <v>30.766000747680664</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -265,19 +277,19 @@
         <v>16</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>39.0</v>
+        <v>2.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>21.0</v>
+        <v>2.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -286,27 +298,27 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>32.19300079345703</v>
+        <v>67.66899108886719</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>2.0</v>
@@ -318,7 +330,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>70.95399475097656</v>
+        <v>70.10700225830078</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>0</v>
@@ -326,16 +338,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>8.0</v>
@@ -350,24 +362,24 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>92.78900146484375</v>
+        <v>93.3290023803711</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>23</v>
-      </c>
       <c r="C7" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>15.0</v>
+        <v>42.0</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>8.0</v>
@@ -382,27 +394,27 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>92.75499725341797</v>
+        <v>93.48799133300781</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>43.0</v>
+        <v>96.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="F8" t="n" s="0">
         <v>3.0</v>
@@ -414,27 +426,27 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>92.17401123046875</v>
+        <v>92.93299865722656</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>15.0</v>
+        <v>127.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="F9" t="n" s="0">
         <v>3.0</v>
@@ -446,28 +458,28 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>92.23100280761719</v>
+        <v>92.7959976196289</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n" s="0">
+        <v>68.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
         <v>15.0</v>
       </c>
-      <c r="E10" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="F10" t="n" s="0">
         <v>1.0</v>
       </c>
@@ -478,10 +490,42 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>92.31800079345703</v>
+        <v>92.37799072265625</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>85.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>122.69500732421875</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
